--- a/data/result1.xlsx
+++ b/data/result1.xlsx
@@ -1,109 +1,437 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="libxl" lastEdited="7" lowestEdited="6" rupBuild="4.6.0"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2024-5-1\数学建模竞赛组委会、专家组工作\竞赛2025\A题-烟幕干扰弹投放策略\2025-8-25 A题(蔡志杰)\附件\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkPlace\2025-gaojiaoshe-A-code\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCD9C1E-C85C-41A1-96D3-F1E5A00FBEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" fullCalcOnLoad="true"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="44" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>无人机运动方向</t>
+  </si>
+  <si>
+    <t>无人机运动速度 (m/s)</t>
+  </si>
+  <si>
+    <t>烟幕干扰弹编号</t>
+  </si>
   <si>
     <t>烟幕干扰弹投放点的x坐标 (m)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无人机运动方向</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>烟幕干扰弹投放点的y坐标 (m)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>烟幕干扰弹投放点的z坐标 (m)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>烟幕干扰弹起爆点的x坐标 (m)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>烟幕干扰弹起爆点的y坐标 (m)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>烟幕干扰弹起爆点的z坐标 (m)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>有效干扰时长 (s)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无人机运动速度 (m/s)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>烟幕干扰弹编号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>注：以x轴为正向，逆时针方向为正，取值0~360（度）。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -111,10 +439,251 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -122,35 +691,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -192,7 +807,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -225,26 +840,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -277,23 +875,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -301,7 +882,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -325,9 +906,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -351,7 +932,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -386,7 +967,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -404,7 +985,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -429,7 +1010,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -455,189 +1036,179 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="13.75" customWidth="true"/>
-    <col min="2" max="2" width="18.25" customWidth="true"/>
-    <col min="4" max="4" width="25" customWidth="true"/>
-    <col min="3" max="3" width="13.75" customWidth="true"/>
-    <col min="5" max="5" width="25" customWidth="true"/>
-    <col min="6" max="6" width="25" customWidth="true"/>
-    <col min="7" max="7" width="25" customWidth="true"/>
-    <col min="8" max="8" width="25" customWidth="true"/>
-    <col min="9" max="9" width="25" customWidth="true"/>
-    <col min="10" max="10" width="14.1640625" customWidth="true"/>
+    <col min="1" max="1" width="13.75" customWidth="1"/>
+    <col min="2" max="2" width="18.25" customWidth="1"/>
+    <col min="3" max="3" width="13.75" customWidth="1"/>
+    <col min="4" max="9" width="25" customWidth="1"/>
+    <col min="10" max="10" width="14.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" s="2" customFormat="true" ht="28" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:10">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" s="3">
-        <v>179.63933775178825</v>
+        <v>179.639337751788</v>
       </c>
       <c r="B2" s="3">
-        <v>137.91572567871154</v>
+        <v>137.915725678712</v>
       </c>
       <c r="C2" s="3">
         <v>1</v>
       </c>
-      <c r="D2" s="0">
-        <v>17792.48843847424</v>
-      </c>
-      <c r="E2" s="0">
-        <v>0.047283979258974852</v>
-      </c>
-      <c r="F2" s="0">
+      <c r="D2" s="4">
+        <v>17792.4884384742</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.0472839792589749</v>
+      </c>
+      <c r="F2" s="4">
         <v>1800</v>
       </c>
-      <c r="G2" s="0">
-        <v>17290.547099293744</v>
-      </c>
-      <c r="H2" s="0">
-        <v>3.2069178036833415</v>
-      </c>
-      <c r="I2" s="0">
-        <v>1735.092984417789</v>
-      </c>
-      <c r="J2" s="0">
-        <v>3.7549999999999999</v>
+      <c r="G2" s="4">
+        <v>17290.5470992937</v>
+      </c>
+      <c r="H2" s="4">
+        <v>3.20691780368334</v>
+      </c>
+      <c r="I2" s="4">
+        <v>1735.09298441779</v>
+      </c>
+      <c r="J2" s="4">
+        <v>3.755</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" s="3">
-        <v>179.63933775178825</v>
+        <v>179.639337751788</v>
       </c>
       <c r="B3" s="3">
-        <v>137.91572567871154</v>
+        <v>137.915725678712</v>
       </c>
       <c r="C3" s="3">
         <v>2</v>
       </c>
-      <c r="D3" s="0">
-        <v>17350.435339838477</v>
-      </c>
-      <c r="E3" s="0">
-        <v>2.8299316984557077</v>
-      </c>
-      <c r="F3" s="0">
+      <c r="D3" s="4">
+        <v>17350.4353398385</v>
+      </c>
+      <c r="E3" s="4">
+        <v>2.82993169845571</v>
+      </c>
+      <c r="F3" s="4">
         <v>1800</v>
       </c>
-      <c r="G3" s="0">
-        <v>16645.380514409542</v>
-      </c>
-      <c r="H3" s="0">
-        <v>7.2681297519095454</v>
-      </c>
-      <c r="I3" s="0">
-        <v>1671.9346946790738</v>
-      </c>
-      <c r="J3" s="0">
-        <v>2.8900000000000001</v>
+      <c r="G3" s="4">
+        <v>16645.3805144095</v>
+      </c>
+      <c r="H3" s="4">
+        <v>7.26812975190955</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1671.93469467907</v>
+      </c>
+      <c r="J3" s="4">
+        <v>2.89</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" s="3">
-        <v>179.63933775178825</v>
+        <v>179.639337751788</v>
       </c>
       <c r="B4" s="3">
-        <v>137.91572567871154</v>
+        <v>137.915725678712</v>
       </c>
       <c r="C4" s="3">
         <v>3</v>
       </c>
-      <c r="D4" s="0">
-        <v>17066.152590982838</v>
-      </c>
-      <c r="E4" s="0">
-        <v>4.6194423820171187</v>
-      </c>
-      <c r="F4" s="0">
+      <c r="D4" s="4">
+        <v>17066.1525909828</v>
+      </c>
+      <c r="E4" s="4">
+        <v>4.61944238201712</v>
+      </c>
+      <c r="F4" s="4">
         <v>1800</v>
       </c>
-      <c r="G4" s="0">
-        <v>16249.401227198914</v>
-      </c>
-      <c r="H4" s="0">
-        <v>9.7607508053674437</v>
-      </c>
-      <c r="I4" s="0">
-        <v>1628.1437039664663</v>
-      </c>
-      <c r="J4" s="0">
-        <v>1.3300000000000001</v>
+      <c r="G4" s="4">
+        <v>16249.4012271989</v>
+      </c>
+      <c r="H4" s="4">
+        <v>9.76075080536744</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1628.14370396647</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1.33</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="0"/>
-      <c r="E5" s="0"/>
-      <c r="F5" s="0"/>
-      <c r="G5" s="0"/>
-      <c r="H5" s="0"/>
-      <c r="I5" s="0"/>
-      <c r="J5" s="0"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" ht="65.4" customHeight="true" x14ac:dyDescent="0.3">
+    <row r="6" ht="65.4" customHeight="1" spans="1:10">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0"/>
-      <c r="C6" s="0"/>
-      <c r="D6" s="0"/>
-      <c r="E6" s="0"/>
-      <c r="F6" s="0"/>
-      <c r="G6" s="0"/>
-      <c r="H6" s="0"/>
-      <c r="I6" s="0"/>
-      <c r="J6" s="0"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>